--- a/artfynd/A 26107-2025 artfynd.xlsx
+++ b/artfynd/A 26107-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4759,6 +4759,618 @@
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131422828</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80355</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Berghem, Berghem, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>668269</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7396499</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Löv-och hänglavsrik, barrblandad naturskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131423771</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57991</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Berghem, Berghem, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>668443</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7396610</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Löv-och hänglavsrik, barrblandad naturskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131423842</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79839</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Berghem, Berghem, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>668462</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7396636</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Löv-och hänglavsrik, barrblandad naturskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131422971</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>864</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Berghem, Berghem, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>668353</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7396491</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Löv-och hänglavsrik, barrblandad naturskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131422918</v>
+      </c>
+      <c r="B46" t="n">
+        <v>83229</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Berghem, Berghem, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>668342</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7396499</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Löv-och hänglavsrik, barrblandad naturskog</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131423003</v>
+      </c>
+      <c r="B47" t="n">
+        <v>83095</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Berghem, Berghem, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>668336</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7396451</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Löv-och hänglavsrik, barrblandad naturskog</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26107-2025 artfynd.xlsx
+++ b/artfynd/A 26107-2025 artfynd.xlsx
@@ -4764,7 +4764,7 @@
         <v>131422828</v>
       </c>
       <c r="B42" t="n">
-        <v>80355</v>
+        <v>80356</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>131423771</v>
       </c>
       <c r="B43" t="n">
-        <v>57991</v>
+        <v>57992</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>131423842</v>
       </c>
       <c r="B44" t="n">
-        <v>79839</v>
+        <v>79840</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>131422971</v>
       </c>
       <c r="B45" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>131422918</v>
       </c>
       <c r="B46" t="n">
-        <v>83229</v>
+        <v>83230</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>131423003</v>
       </c>
       <c r="B47" t="n">
-        <v>83095</v>
+        <v>83096</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 26107-2025 artfynd.xlsx
+++ b/artfynd/A 26107-2025 artfynd.xlsx
@@ -4764,7 +4764,7 @@
         <v>131422828</v>
       </c>
       <c r="B42" t="n">
-        <v>80356</v>
+        <v>80359</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>131423771</v>
       </c>
       <c r="B43" t="n">
-        <v>57992</v>
+        <v>57995</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>131423842</v>
       </c>
       <c r="B44" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>131422971</v>
       </c>
       <c r="B45" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>131422918</v>
       </c>
       <c r="B46" t="n">
-        <v>83230</v>
+        <v>83233</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>131423003</v>
       </c>
       <c r="B47" t="n">
-        <v>83096</v>
+        <v>83099</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 26107-2025 artfynd.xlsx
+++ b/artfynd/A 26107-2025 artfynd.xlsx
@@ -4764,7 +4764,7 @@
         <v>131422828</v>
       </c>
       <c r="B42" t="n">
-        <v>80359</v>
+        <v>80360</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>131423771</v>
       </c>
       <c r="B43" t="n">
-        <v>57995</v>
+        <v>57996</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>131423842</v>
       </c>
       <c r="B44" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>131422971</v>
       </c>
       <c r="B45" t="n">
-        <v>79332</v>
+        <v>79333</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>131422918</v>
       </c>
       <c r="B46" t="n">
-        <v>83233</v>
+        <v>83234</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>131423003</v>
       </c>
       <c r="B47" t="n">
-        <v>83099</v>
+        <v>83100</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 26107-2025 artfynd.xlsx
+++ b/artfynd/A 26107-2025 artfynd.xlsx
@@ -4764,7 +4764,7 @@
         <v>131422828</v>
       </c>
       <c r="B42" t="n">
-        <v>80360</v>
+        <v>80366</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>131423771</v>
       </c>
       <c r="B43" t="n">
-        <v>57996</v>
+        <v>58002</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>131423842</v>
       </c>
       <c r="B44" t="n">
-        <v>79844</v>
+        <v>79850</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>131422971</v>
       </c>
       <c r="B45" t="n">
-        <v>79333</v>
+        <v>79339</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>131422918</v>
       </c>
       <c r="B46" t="n">
-        <v>83234</v>
+        <v>83240</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>131423003</v>
       </c>
       <c r="B47" t="n">
-        <v>83100</v>
+        <v>83106</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 26107-2025 artfynd.xlsx
+++ b/artfynd/A 26107-2025 artfynd.xlsx
@@ -4764,7 +4764,7 @@
         <v>131422828</v>
       </c>
       <c r="B42" t="n">
-        <v>80366</v>
+        <v>80367</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>131423771</v>
       </c>
       <c r="B43" t="n">
-        <v>58002</v>
+        <v>58003</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>131423842</v>
       </c>
       <c r="B44" t="n">
-        <v>79850</v>
+        <v>79851</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>131422971</v>
       </c>
       <c r="B45" t="n">
-        <v>79339</v>
+        <v>79340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>131422918</v>
       </c>
       <c r="B46" t="n">
-        <v>83240</v>
+        <v>83241</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>131423003</v>
       </c>
       <c r="B47" t="n">
-        <v>83106</v>
+        <v>83107</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 26107-2025 artfynd.xlsx
+++ b/artfynd/A 26107-2025 artfynd.xlsx
@@ -4764,7 +4764,7 @@
         <v>131422828</v>
       </c>
       <c r="B42" t="n">
-        <v>80367</v>
+        <v>80370</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>131423771</v>
       </c>
       <c r="B43" t="n">
-        <v>58003</v>
+        <v>58006</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>131423842</v>
       </c>
       <c r="B44" t="n">
-        <v>79851</v>
+        <v>79854</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>131422971</v>
       </c>
       <c r="B45" t="n">
-        <v>79340</v>
+        <v>79343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>131422918</v>
       </c>
       <c r="B46" t="n">
-        <v>83241</v>
+        <v>83244</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>131423003</v>
       </c>
       <c r="B47" t="n">
-        <v>83107</v>
+        <v>83110</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 26107-2025 artfynd.xlsx
+++ b/artfynd/A 26107-2025 artfynd.xlsx
@@ -4764,7 +4764,7 @@
         <v>131422828</v>
       </c>
       <c r="B42" t="n">
-        <v>80370</v>
+        <v>80372</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>131423771</v>
       </c>
       <c r="B43" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>131423842</v>
       </c>
       <c r="B44" t="n">
-        <v>79854</v>
+        <v>79856</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>131422971</v>
       </c>
       <c r="B45" t="n">
-        <v>79343</v>
+        <v>79345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>131422918</v>
       </c>
       <c r="B46" t="n">
-        <v>83244</v>
+        <v>83246</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>131423003</v>
       </c>
       <c r="B47" t="n">
-        <v>83110</v>
+        <v>83112</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 26107-2025 artfynd.xlsx
+++ b/artfynd/A 26107-2025 artfynd.xlsx
@@ -4764,7 +4764,7 @@
         <v>131422828</v>
       </c>
       <c r="B42" t="n">
-        <v>80372</v>
+        <v>80375</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>131423771</v>
       </c>
       <c r="B43" t="n">
-        <v>58008</v>
+        <v>58011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>131423842</v>
       </c>
       <c r="B44" t="n">
-        <v>79856</v>
+        <v>79859</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>131422971</v>
       </c>
       <c r="B45" t="n">
-        <v>79345</v>
+        <v>79348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>131422918</v>
       </c>
       <c r="B46" t="n">
-        <v>83246</v>
+        <v>83249</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>131423003</v>
       </c>
       <c r="B47" t="n">
-        <v>83112</v>
+        <v>83115</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 26107-2025 artfynd.xlsx
+++ b/artfynd/A 26107-2025 artfynd.xlsx
@@ -4764,7 +4764,7 @@
         <v>131422828</v>
       </c>
       <c r="B42" t="n">
-        <v>80375</v>
+        <v>80380</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>131423771</v>
       </c>
       <c r="B43" t="n">
-        <v>58011</v>
+        <v>58016</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>131423842</v>
       </c>
       <c r="B44" t="n">
-        <v>79859</v>
+        <v>79864</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>131422971</v>
       </c>
       <c r="B45" t="n">
-        <v>79348</v>
+        <v>79353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>131422918</v>
       </c>
       <c r="B46" t="n">
-        <v>83249</v>
+        <v>83254</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>131423003</v>
       </c>
       <c r="B47" t="n">
-        <v>83115</v>
+        <v>83120</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 26107-2025 artfynd.xlsx
+++ b/artfynd/A 26107-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119302486</v>
+        <v>119358579</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668522</v>
+        <v>668643</v>
       </c>
       <c r="R2" t="n">
-        <v>7396791</v>
+        <v>7396072</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson, Elin Götmark, Linda Hanson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119302496</v>
+        <v>119326528</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Luspevárásj, Lu lm</t>
+          <t>Luspevarasj, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668544</v>
+        <v>668614</v>
       </c>
       <c r="R3" t="n">
-        <v>7396496</v>
+        <v>7396103</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,65 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Lisa Behrenfeldt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Lisa Behrenfeldt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119302500</v>
+        <v>119320528</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hypogymnia austerodes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Räsänen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Luspevárásj, Lu lm</t>
+          <t>Luspevarasj, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668580</v>
+        <v>668557</v>
       </c>
       <c r="R4" t="n">
-        <v>7396613</v>
+        <v>7396739</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119302499</v>
+        <v>119302494</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668587</v>
+        <v>668649</v>
       </c>
       <c r="R5" t="n">
-        <v>7396596</v>
+        <v>7396025</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,12 +1066,7 @@
         <v>119302495</v>
       </c>
       <c r="B6" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119302490</v>
+        <v>119302496</v>
       </c>
       <c r="B7" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668593</v>
+        <v>668544</v>
       </c>
       <c r="R7" t="n">
-        <v>7396556</v>
+        <v>7396496</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119302498</v>
+        <v>119302497</v>
       </c>
       <c r="B8" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668595</v>
+        <v>668601</v>
       </c>
       <c r="R8" t="n">
-        <v>7396561</v>
+        <v>7396547</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119302487</v>
+        <v>119302498</v>
       </c>
       <c r="B9" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668472</v>
+        <v>668595</v>
       </c>
       <c r="R9" t="n">
-        <v>7396236</v>
+        <v>7396561</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119320535</v>
+        <v>119302499</v>
       </c>
       <c r="B10" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,17 +1482,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Luspevarasj, Lu lm</t>
+          <t>Luspevárásj, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668541</v>
+        <v>668587</v>
       </c>
       <c r="R10" t="n">
-        <v>7396491</v>
+        <v>7396596</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1581,27 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119320541</v>
+        <v>119302500</v>
       </c>
       <c r="B11" t="n">
-        <v>90558</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,37 +1559,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Luspevarasj, Lu lm</t>
+          <t>Luspevárásj, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668539</v>
+        <v>668580</v>
       </c>
       <c r="R11" t="n">
-        <v>7396651</v>
+        <v>7396613</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1683,27 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119320548</v>
+        <v>119320530</v>
       </c>
       <c r="B12" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668606</v>
+        <v>668646</v>
       </c>
       <c r="R12" t="n">
-        <v>7396577</v>
+        <v>7396043</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119320547</v>
+        <v>119320531</v>
       </c>
       <c r="B13" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668543</v>
+        <v>668652</v>
       </c>
       <c r="R13" t="n">
-        <v>7396489</v>
+        <v>7396064</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119320536</v>
+        <v>119320535</v>
       </c>
       <c r="B14" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668600</v>
+        <v>668541</v>
       </c>
       <c r="R14" t="n">
-        <v>7396565</v>
+        <v>7396491</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119320537</v>
+        <v>119320536</v>
       </c>
       <c r="B15" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668606</v>
+        <v>668600</v>
       </c>
       <c r="R15" t="n">
-        <v>7396584</v>
+        <v>7396565</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119320512</v>
+        <v>119320537</v>
       </c>
       <c r="B16" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668529</v>
+        <v>668606</v>
       </c>
       <c r="R16" t="n">
-        <v>7396416</v>
+        <v>7396584</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119320555</v>
+        <v>119320538</v>
       </c>
       <c r="B17" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668560</v>
+        <v>668557</v>
       </c>
       <c r="R17" t="n">
-        <v>7396488</v>
+        <v>7396723</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119320538</v>
+        <v>119326529</v>
       </c>
       <c r="B18" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668557</v>
+        <v>668610</v>
       </c>
       <c r="R18" t="n">
-        <v>7396723</v>
+        <v>7396061</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2397,27 +2312,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lisa Behrenfeldt</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lisa Behrenfeldt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119320514</v>
+        <v>119326530</v>
       </c>
       <c r="B19" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668479</v>
+        <v>668601</v>
       </c>
       <c r="R19" t="n">
-        <v>7396817</v>
+        <v>7396542</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2499,49 +2409,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lisa Behrenfeldt</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lisa Behrenfeldt</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119320528</v>
+        <v>119326531</v>
       </c>
       <c r="B20" t="n">
-        <v>78607</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk blåslav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia austerodes</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Räsänen</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668557</v>
+        <v>668520</v>
       </c>
       <c r="R20" t="n">
-        <v>7396739</v>
+        <v>7396764</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2601,27 +2506,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lisa Behrenfeldt</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lisa Behrenfeldt</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119326531</v>
+        <v>119358593</v>
       </c>
       <c r="B21" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2649,14 +2549,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Luspevarasj, Lu lm</t>
+          <t>Luspevárásj, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668520</v>
+        <v>668639</v>
       </c>
       <c r="R21" t="n">
-        <v>7396764</v>
+        <v>7396033</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2703,27 +2603,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lisa Behrenfeldt</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Behrenfeldt</t>
+          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119326528</v>
+        <v>119358594</v>
       </c>
       <c r="B22" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,34 +2626,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Luspevarasj, Lu lm</t>
+          <t>Luspevárásj, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668614</v>
+        <v>668637</v>
       </c>
       <c r="R22" t="n">
-        <v>7396103</v>
+        <v>7396617</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2805,27 +2700,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lisa Behrenfeldt</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lisa Behrenfeldt</t>
+          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119326529</v>
+        <v>119358595</v>
       </c>
       <c r="B23" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,14 +2743,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Luspevarasj, Lu lm</t>
+          <t>Luspevárásj, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668610</v>
+        <v>668573</v>
       </c>
       <c r="R23" t="n">
-        <v>7396061</v>
+        <v>7396718</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2907,27 +2797,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lisa Behrenfeldt</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lisa Behrenfeldt</t>
+          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119358594</v>
+        <v>119358596</v>
       </c>
       <c r="B24" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668637</v>
+        <v>668562</v>
       </c>
       <c r="R24" t="n">
-        <v>7396617</v>
+        <v>7396725</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,37 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119358610</v>
+        <v>119358597</v>
       </c>
       <c r="B25" t="n">
-        <v>79642</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668530</v>
+        <v>668505</v>
       </c>
       <c r="R25" t="n">
-        <v>7396732</v>
+        <v>7396802</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,53 +3003,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119358612</v>
+        <v>120055745</v>
       </c>
       <c r="B26" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Luspevárásj, Lu lm</t>
+          <t>Luspevarasj, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668561</v>
+        <v>668632</v>
       </c>
       <c r="R26" t="n">
-        <v>7396732</v>
+        <v>7396071</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3213,62 +3088,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Maria Brandt</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
+          <t>Maria Brandt</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119358586</v>
+        <v>131422971</v>
       </c>
       <c r="B27" t="n">
-        <v>96862</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Luspevárásj, Lu lm</t>
+          <t>Berghem, Berghem, Lu lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668475</v>
+        <v>668353</v>
       </c>
       <c r="R27" t="n">
-        <v>7396849</v>
+        <v>7396491</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3295,12 +3165,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3311,31 +3181,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Löv-och hänglavsrik, barrblandad naturskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119358595</v>
+        <v>119320541</v>
       </c>
       <c r="B28" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3343,34 +3213,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Luspevárásj, Lu lm</t>
+          <t>Luspevarasj, Lu lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668573</v>
+        <v>668539</v>
       </c>
       <c r="R28" t="n">
-        <v>7396718</v>
+        <v>7396651</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3417,27 +3287,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119358596</v>
+        <v>119320545</v>
       </c>
       <c r="B29" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3445,34 +3310,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Luspevárásj, Lu lm</t>
+          <t>Luspevarasj, Lu lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668562</v>
+        <v>668648</v>
       </c>
       <c r="R29" t="n">
-        <v>7396725</v>
+        <v>7396053</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3519,27 +3384,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119358605</v>
+        <v>119320547</v>
       </c>
       <c r="B30" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3567,14 +3427,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Luspevárásj, Lu lm</t>
+          <t>Luspevarasj, Lu lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668555</v>
+        <v>668543</v>
       </c>
       <c r="R30" t="n">
-        <v>7396729</v>
+        <v>7396489</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3621,62 +3481,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119358613</v>
+        <v>119320548</v>
       </c>
       <c r="B31" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Luspevárásj, Lu lm</t>
+          <t>Luspevarasj, Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668538</v>
+        <v>668606</v>
       </c>
       <c r="R31" t="n">
-        <v>7396755</v>
+        <v>7396577</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3723,27 +3578,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119358619</v>
+        <v>119358604</v>
       </c>
       <c r="B32" t="n">
-        <v>77910</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3751,21 +3601,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668665</v>
+        <v>668633</v>
       </c>
       <c r="R32" t="n">
-        <v>7396614</v>
+        <v>7396080</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,15 +3687,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119358585</v>
+        <v>119358605</v>
       </c>
       <c r="B33" t="n">
-        <v>74643</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,21 +3698,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668450</v>
+        <v>668555</v>
       </c>
       <c r="R33" t="n">
-        <v>7396858</v>
+        <v>7396729</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,15 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119358580</v>
+        <v>131423003</v>
       </c>
       <c r="B34" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3955,34 +3795,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Luspevárásj, Lu lm</t>
+          <t>Berghem, Berghem, Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668538</v>
+        <v>668336</v>
       </c>
       <c r="R34" t="n">
-        <v>7396756</v>
+        <v>7396451</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4009,12 +3849,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4025,31 +3865,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Löv-och hänglavsrik, barrblandad naturskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson, Elin Götmark, Linda Hanson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119358560</v>
+        <v>119358585</v>
       </c>
       <c r="B35" t="n">
-        <v>79144</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4057,21 +3897,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>1467</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +3921,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668677</v>
+        <v>668450</v>
       </c>
       <c r="R35" t="n">
-        <v>7396604</v>
+        <v>7396858</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,15 +3983,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119358597</v>
+        <v>119302490</v>
       </c>
       <c r="B36" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4159,21 +3994,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4183,13 +4018,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668505</v>
+        <v>668593</v>
       </c>
       <c r="R36" t="n">
-        <v>7396802</v>
+        <v>7396556</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4233,27 +4068,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119358568</v>
+        <v>119358580</v>
       </c>
       <c r="B37" t="n">
-        <v>79115</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4261,21 +4091,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4115,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668669</v>
+        <v>668538</v>
       </c>
       <c r="R37" t="n">
-        <v>7396610</v>
+        <v>7396756</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4340,22 +4170,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
+          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson, Elin Götmark, Linda Hanson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119358558</v>
+        <v>131422828</v>
       </c>
       <c r="B38" t="n">
-        <v>74638</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4363,34 +4188,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Luspevárásj, Lu lm</t>
+          <t>Berghem, Berghem, Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668448</v>
+        <v>668269</v>
       </c>
       <c r="R38" t="n">
-        <v>7396850</v>
+        <v>7396499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4417,12 +4242,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4433,31 +4258,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Löv-och hänglavsrik, barrblandad naturskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120055747</v>
+        <v>119326535</v>
       </c>
       <c r="B39" t="n">
-        <v>79658</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4465,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>4217</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,13 +4314,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668535</v>
+        <v>668620</v>
       </c>
       <c r="R39" t="n">
-        <v>7396735</v>
+        <v>7396107</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4533,34 +4358,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Maria Brandt</t>
+          <t>Lisa Behrenfeldt</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Maria Brandt</t>
+          <t>Lisa Behrenfeldt</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120055745</v>
+        <v>119358619</v>
       </c>
       <c r="B40" t="n">
-        <v>78624</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4568,37 +4387,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>864</v>
+        <v>6437</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Luspevarasj, Lu lm</t>
+          <t>Luspevárásj, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668632</v>
+        <v>668665</v>
       </c>
       <c r="R40" t="n">
-        <v>7396071</v>
+        <v>7396614</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4642,27 +4461,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Maria Brandt</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Maria Brandt</t>
+          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120055736</v>
+        <v>119358558</v>
       </c>
       <c r="B41" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4670,37 +4484,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Luspevarasj, Lu lm</t>
+          <t>Luspevárásj, Lu lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668522</v>
+        <v>668448</v>
       </c>
       <c r="R41" t="n">
-        <v>7396787</v>
+        <v>7396850</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4730,11 +4544,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-08-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hackmärken på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4749,22 +4558,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Maria Brandt</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Maria Brandt</t>
+          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131422828</v>
+        <v>131422918</v>
       </c>
       <c r="B42" t="n">
-        <v>80380</v>
+        <v>83307</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,21 +4581,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4796,7 +4605,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668269</v>
+        <v>668342</v>
       </c>
       <c r="R42" t="n">
         <v>7396499</v>
@@ -4863,48 +4672,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131423771</v>
+        <v>119358560</v>
       </c>
       <c r="B43" t="n">
-        <v>58016</v>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Berghem, Berghem, Lu lm</t>
+          <t>Luspevárásj, Lu lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668443</v>
+        <v>668677</v>
       </c>
       <c r="R43" t="n">
-        <v>7396610</v>
+        <v>7396604</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4928,12 +4737,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4944,66 +4753,61 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Löv-och hänglavsrik, barrblandad naturskog</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131423842</v>
+        <v>119358610</v>
       </c>
       <c r="B44" t="n">
-        <v>79864</v>
+        <v>80467</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Berghem, Berghem, Lu lm</t>
+          <t>Luspevárásj, Lu lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668462</v>
+        <v>668530</v>
       </c>
       <c r="R44" t="n">
-        <v>7396636</v>
+        <v>7396732</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5030,12 +4834,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5046,69 +4850,64 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Löv-och hänglavsrik, barrblandad naturskog</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131422971</v>
+        <v>120055747</v>
       </c>
       <c r="B45" t="n">
-        <v>79353</v>
+        <v>80467</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>864</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Berghem, Berghem, Lu lm</t>
+          <t>Luspevarasj, Lu lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668353</v>
+        <v>668535</v>
       </c>
       <c r="R45" t="n">
-        <v>7396491</v>
+        <v>7396735</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5132,12 +4931,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5146,33 +4945,29 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Löv-och hänglavsrik, barrblandad naturskog</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Maria Brandt</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Maria Brandt</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131422918</v>
+        <v>119302486</v>
       </c>
       <c r="B46" t="n">
-        <v>83254</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5180,37 +4975,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Berghem, Berghem, Lu lm</t>
+          <t>Luspevárásj, Lu lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668342</v>
+        <v>668522</v>
       </c>
       <c r="R46" t="n">
-        <v>7396499</v>
+        <v>7396791</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5234,12 +5029,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5250,31 +5045,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Löv-och hänglavsrik, barrblandad naturskog</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131423003</v>
+        <v>120055736</v>
       </c>
       <c r="B47" t="n">
-        <v>83120</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5282,37 +5072,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Berghem, Berghem, Lu lm</t>
+          <t>Luspevarasj, Lu lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>668336</v>
+        <v>668522</v>
       </c>
       <c r="R47" t="n">
-        <v>7396451</v>
+        <v>7396787</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5336,12 +5126,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Hackmärken på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5352,24 +5147,805 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Löv-och hänglavsrik, barrblandad naturskog</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
+          <t>Maria Brandt</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Maria Brandt</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>119320555</v>
+      </c>
+      <c r="B48" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Luspevarasj, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>668560</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7396488</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>119358612</v>
+      </c>
+      <c r="B49" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Luspevárásj, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>668561</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7396732</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>119358613</v>
+      </c>
+      <c r="B50" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Luspevárásj, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>668538</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7396755</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>119320514</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Luspevarasj, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>668479</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7396817</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>131423771</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Berghem, Berghem, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>668443</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7396610</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Löv-och hänglavsrik, barrblandad naturskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
           <t>Rashid Kadhim</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
+      <c r="AX52" t="inlineStr">
         <is>
           <t>Rashid Kadhim</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>119358586</v>
+      </c>
+      <c r="B53" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Luspevárásj, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>668475</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7396849</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>119358568</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Luspevárásj, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>668669</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7396610</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba, Elin Götmark, Linda Hanson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>131423842</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Berghem, Berghem, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>668462</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7396636</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Löv-och hänglavsrik, barrblandad naturskog</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26107-2025 artfynd.xlsx
+++ b/artfynd/A 26107-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358579</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119326528</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119320528</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119302494</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119302495</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119302496</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119302497</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119302498</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119302499</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119302500</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119320530</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119320531</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119320535</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119320536</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119320537</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119320538</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119326529</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119326530</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119326531</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358593</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358594</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358595</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358596</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358597</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120055745</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3199,6 +3329,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131422971</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3296,6 +3431,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119320541</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3393,6 +3533,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119320545</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3490,6 +3635,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119320547</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3587,6 +3737,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119320548</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3684,6 +3839,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358604</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3781,6 +3941,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358605</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3883,6 +4048,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131423003</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3980,6 +4150,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358585</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4077,6 +4252,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119302490</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4174,6 +4354,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358580</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4276,6 +4461,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131422828</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4373,6 +4563,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119326535</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4470,6 +4665,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358619</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4567,6 +4767,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358558</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4669,6 +4874,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131422918</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4766,6 +4976,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358560</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4863,6 +5078,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358610</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4961,6 +5181,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120055747</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5058,6 +5283,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119302486</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5160,6 +5390,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120055736</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5257,6 +5492,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119320555</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5354,6 +5594,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358612</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5451,6 +5696,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358613</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5548,6 +5798,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119320514</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5650,6 +5905,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131423771</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5747,6 +6007,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358586</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5844,6 +6109,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358568</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5946,8 +6216,69 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131423842</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>